--- a/data/raw/inventory/Week 27/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -5793,7 +5793,7 @@
         <v>186</v>
       </c>
       <c r="F87" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
         <v>187</v>
@@ -7963,7 +7963,7 @@
         <v>128</v>
       </c>
       <c r="F122" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -7975,7 +7975,7 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
         <v>128</v>
@@ -11373,7 +11373,7 @@
         <v>13</v>
       </c>
       <c r="F177" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11385,7 +11385,7 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" t="n">
         <v>13</v>

--- a/data/raw/inventory/Week 27/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 27/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -523,7 +523,7 @@
         <v>156</v>
       </c>
       <c r="F2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>156</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1096,7 +1096,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F36" t="n">
         <v>68</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
         <v>27</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3635,10 +3635,10 @@
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F62" t="n">
         <v>18</v>
@@ -4255,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -4491,7 +4491,7 @@
         <v>23</v>
       </c>
       <c r="F66" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>23</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F68" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F79" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L79" t="n">
         <v>1</v>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F83" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F84" t="n">
         <v>65</v>
@@ -5619,10 +5619,10 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
@@ -5790,25 +5790,25 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F87" t="n">
+        <v>182</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K87" t="n">
         <v>185</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>187</v>
       </c>
       <c r="L87" t="n">
         <v>1</v>
@@ -5855,7 +5855,7 @@
         <v>40</v>
       </c>
       <c r="F88" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5867,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
         <v>40</v>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F106" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K106" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -7464,10 +7464,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F114" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7479,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7591,7 +7591,7 @@
         <v>14</v>
       </c>
       <c r="F116" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K116" t="n">
         <v>14</v>
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F125" t="n">
         <v>51</v>
@@ -8161,10 +8161,10 @@
         <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
@@ -8273,7 +8273,7 @@
         <v>96</v>
       </c>
       <c r="F127" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
         <v>97</v>
@@ -8831,7 +8831,7 @@
         <v>10</v>
       </c>
       <c r="F136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -8843,13 +8843,13 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
@@ -9017,7 +9017,7 @@
         <v>20</v>
       </c>
       <c r="F139" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>20</v>
@@ -9324,7 +9324,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F144" t="n">
         <v>47</v>
@@ -9339,10 +9339,10 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K144" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F177" t="n">
         <v>12</v>
@@ -11385,10 +11385,10 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11447,10 +11447,10 @@
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="L178" t="n">
         <v>2</v>
